--- a/xbd.WarehouseTHPro/Config/仓储A区_COM1_9600_None_8_One.xlsx
+++ b/xbd.WarehouseTHPro/Config/仓储A区_COM1_9600_None_8_One.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\.netStudy\winforms\温湿度监控系统\xbd.WarehouseTHPro\xbd.WarehouseTHPro\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73590F41-0DE0-40F6-937C-56AA0B9DA458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DA63E1A-5C33-4345-9564-4DE4E81C9688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="A01_保持寄存器_1_0_6" sheetId="1" r:id="rId1"/>
@@ -583,6 +583,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
